--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255829억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255830억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267881억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 267918억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275698억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 275771억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 277286억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 278191억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275969억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 276892억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273608억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 274512억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 270406억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 271292억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267324억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 267395억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 262944억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263015억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257140억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 257212억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4528억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4529억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4822억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4824억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5137억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5140억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5335억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5339억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5634억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5637억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5928억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5931억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1797,61 +1797,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255829억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255830억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267881억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267918억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275698억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 275771억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 277286억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 278191억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275969억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 276892억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273608억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 274512억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 270406억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 271292억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267324억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267395억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 262944억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263015억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257140억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 257212억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2276,37 +2276,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4528억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4529억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4822억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4824억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5137억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5140억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5335억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5339억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5634억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5637억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5928억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5931억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6593,33 +6593,33 @@
         <v>0.227768</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.370688</v>
+        <v>0.370877</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.349248</v>
+        <v>-0.349076</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.154041</v>
+        <v>0.157811</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.078726</v>
+        <v>0.08233</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.021379</v>
+        <v>0.024616</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.019194</v>
+        <v>-0.016242</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035927</v>
+        <v>-0.03881</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.047204</v>
+        <v>-0.050114</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.060187</v>
+        <v>-0.063023</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6739,39 +6739,39 @@
         <v>0.059291</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.059291</v>
+        <v>0.05929</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.059286</v>
+        <v>0.059293</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.059288</v>
+        <v>0.05929</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.059287</v>
+        <v>0.059289</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.059286</v>
+        <v>0.05929</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.059284</v>
+        <v>0.05929</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.059287</v>
+        <v>0.059286</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.059291</v>
+        <v>0.059289</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.059289</v>
+        <v>0.059286</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6894,39 +6894,39 @@
         <v>0.180909</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.180905</v>
+        <v>0.180906</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
+        <v>0.180908</v>
+      </c>
+      <c r="AG23" s="24" t="n">
+        <v>0.180911</v>
+      </c>
+      <c r="AH23" s="24" t="n">
+        <v>0.180907</v>
+      </c>
+      <c r="AI23" s="24" t="n">
         <v>0.18091</v>
-      </c>
-      <c r="AG23" s="24" t="n">
-        <v>0.180907</v>
-      </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.18091</v>
-      </c>
-      <c r="AI23" s="24" t="n">
-        <v>0.180909</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.180905</v>
+        <v>0.180911</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.180908</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.180908</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.180904</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7181,26 +7181,26 @@
         <v>44.59</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>47.82</v>
+        <v>47.83</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>51.03</v>
+        <v>51.05</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>54.46</v>
+        <v>54.49</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>56.62</v>
+        <v>56.66</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>59.88</v>
+        <v>59.92</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>63.08</v>
+        <v>63.12</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7478,39 +7478,39 @@
         <v>0.049989</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.049992</v>
+        <v>0.049986</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.04999</v>
+        <v>0.049977</v>
       </c>
       <c r="AG27" s="24" t="n">
+        <v>0.050008</v>
+      </c>
+      <c r="AH27" s="24" t="n">
         <v>0.049989</v>
       </c>
-      <c r="AH27" s="24" t="n">
-        <v>0.050002</v>
-      </c>
       <c r="AI27" s="24" t="n">
-        <v>0.049985</v>
+        <v>0.049994</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050007</v>
+        <v>0.050024</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.049984</v>
+        <v>0.05</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.050016</v>
+        <v>0.05</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.049995</v>
+        <v>0.050009</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AG31" s="29" t="n">
         <v>0</v>
@@ -8020,10 +8020,10 @@
         <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN31" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AG32" s="29" t="n">
         <v>0</v>
@@ -8148,10 +8148,10 @@
         <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN32" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8381,33 +8381,33 @@
         <v>0.087099</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.090347</v>
+        <v>0.09035899999999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.052607</v>
+        <v>0.052618</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.078124</v>
+        <v>0.07834099999999999</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.07184</v>
+        <v>0.072029</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.07194299999999999</v>
+        <v>0.07212</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.042151</v>
+        <v>0.042235</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060987</v>
+        <v>0.060968</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.056497</v>
+        <v>0.056478</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.056611</v>
+        <v>0.056597</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8509,33 +8509,33 @@
         <v>0.076169</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.07981100000000001</v>
+        <v>0.079819</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.046926</v>
+        <v>0.046938</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.070065</v>
+        <v>0.07026</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064914</v>
+        <v>0.065086</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06543</v>
+        <v>0.065593</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.038569</v>
+        <v>0.038647</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.055998</v>
+        <v>0.055983</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.05212</v>
+        <v>0.052107</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.052443</v>
+        <v>0.05243</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9168,26 +9168,26 @@
         <v>-0.07037</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>0.108868</v>
+        <v>0.108147</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.841328</v>
+        <v>0.837638</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.062725</v>
+        <v>0.059841</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.028552</v>
+        <v>-0.031873</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.051365</v>
+        <v>-0.0527</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.024716</v>
+        <v>-0.024096</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.005427</v>
+        <v>-0.003401</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9287,7 +9287,7 @@
         <v>-0.5360819999999999</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.5009670000000001</v>
+        <v>-0.502901</v>
       </c>
       <c r="AH42" s="24" t="n">
         <v>-0.163265</v>
@@ -9300,10 +9300,10 @@
         <v>-0.155556</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.151163</v>
+        <v>-0.14786</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.142276</v>
+        <v>-0.146341</v>
       </c>
       <c r="AN42" s="24" t="n">
         <v>-0.140426</v>
@@ -9581,39 +9581,39 @@
         <v>0.180909</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.180905</v>
+        <v>0.180906</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
+        <v>0.180908</v>
+      </c>
+      <c r="AG44" s="24" t="n">
+        <v>0.180911</v>
+      </c>
+      <c r="AH44" s="24" t="n">
+        <v>0.180907</v>
+      </c>
+      <c r="AI44" s="24" t="n">
         <v>0.18091</v>
-      </c>
-      <c r="AG44" s="24" t="n">
-        <v>0.180907</v>
-      </c>
-      <c r="AH44" s="24" t="n">
-        <v>0.18091</v>
-      </c>
-      <c r="AI44" s="24" t="n">
-        <v>0.180909</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.180905</v>
+        <v>0.180911</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.180908</v>
       </c>
       <c r="AM44" s="24" t="n">
         <v>0.180908</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.180904</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -39289,7 +39289,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3094.8</v>
+        <v>3097.4</v>
       </c>
     </row>
     <row r="30">
@@ -39309,7 +39309,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.38</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="32">
@@ -39329,7 +39329,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2011</v>
+        <v>0.2013</v>
       </c>
     </row>
     <row r="34">
@@ -39339,7 +39339,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="35">
@@ -39349,7 +39349,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34300</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$98</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$106</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$96</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255830억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267918억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 275771억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 278191억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 276892억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 274512억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 271292억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267395억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263015억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+9.3%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257212억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+전년동기 × (1+9.3%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 18.1% 유지</t>
+최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,55 +894,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3743억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3770억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4042억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4069억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4231억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4424억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4529억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4770억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4824억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5122억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5140억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5483억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5339억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 5911억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5637억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6328억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 5931억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6725억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1797,61 +1797,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255830억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267918억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 275771억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 278191억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+37.0%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 276892억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 274512억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 271292억 × 비례계수 0.0194 × 계절비중 Q1 0.162(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267395억 × 비례계수 0.0194 × 계절비중 Q2 0.275(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+18.5%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263015억 × 비례계수 0.0194 × 계절비중 Q3 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+9.3%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257212억 × 비례계수 0.0194 × 계절비중 Q4 0.293(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 전년동기 × (1+9.3%) — g=최근 4분기 합 YoY 37.0% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -2037,61 +2037,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2192,61 +2192,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 18.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 18.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2258,55 +2258,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3743억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3770억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4042억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4069억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4231억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4424억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4529억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4770억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4824억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5122억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5140억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5483억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5339억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 5911억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5637억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6328억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 5931억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6725억 × 4.36% − 총차입금 362억 × 1.68% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4535,14 +4535,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 750억(영업이익 279억의 3배, 12분기 중위 34억) → 지배NI 1,121억·EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함)</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 25.2% &gt; 추세 12.9% × 1.10 (suppliers_mentions·시차 0·4분기 이동합·창 8, r=1.00 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 750억(영업이익 279억의 3배, 12분기 중위 34억) → 지배NI 1,121억·EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 25.2, "op_wape_pct": 66.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 962.04, "rev_act": 1091.69, "op_pred": 100.52, "op_act": 202.88}, {"q": "2025Q4", "rev_pred": 1039.09, "rev_act": 1109.76, "op_pred": 108.57, "op_act": 278.89}, {"q": "2026Q1", "rev_pred": 487.33, "rev_act": 1334.61, "op_pred": 50.92, "op_act": 325.64}, {"q": "2026Q2", "rev_pred": 1112.99, "rev_act": 1281.19, "op_pred": 116.29, "op_act": 312.86}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 25.2, "op_wape_pct": 66.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 15.8, "wape_trend": 25.4, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 962.04, "rev_act": 1091.69, "op_pred": 100.52, "op_act": 202.88}, {"q": "2025Q4", "rev_pred": 1039.09, "rev_act": 1109.76, "op_pred": 108.57, "op_act": 278.89}, {"q": "2026Q1", "rev_pred": 487.33, "rev_act": 1334.61, "op_pred": 50.92, "op_act": 325.64}, {"q": "2026Q2", "rev_pred": 1112.99, "rev_act": 1281.19, "op_pred": 116.29, "op_act": 312.86}]}</t>
         </is>
       </c>
     </row>
@@ -6590,36 +6590,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.227768</v>
+        <v>0.370116</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.370877</v>
+        <v>0.370121</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.349076</v>
+        <v>0.370116</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.157811</v>
+        <v>0.37012</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08233</v>
+        <v>0.185059</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.024616</v>
+        <v>0.185058</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.016242</v>
+        <v>0.185063</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.03881</v>
+        <v>0.185059</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.050114</v>
+        <v>0.092528</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.063023</v>
+        <v>0.092526</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6736,7 +6736,7 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.059291</v>
+        <v>0.059288</v>
       </c>
       <c r="AD22" s="24" t="n">
         <v>0.05929</v>
@@ -6746,16 +6746,16 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.059293</v>
+        <v>0.059287</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.05929</v>
+        <v>0.059286</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.059289</v>
+        <v>0.059288</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.05929</v>
+        <v>0.059288</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -6768,7 +6768,7 @@
         <v>0.059286</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.059289</v>
+        <v>0.059286</v>
       </c>
       <c r="AN22" s="24" t="n">
         <v>0.059286</v>
@@ -6891,42 +6891,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.180909</v>
+        <v>0.180907</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.180906</v>
+        <v>0.180908</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180906</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.180911</v>
+        <v>0.180906</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.18091</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.18091</v>
+        <v>0.180905</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.180911</v>
+        <v>0.180907</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180907</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180909</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.180904</v>
+        <v>0.18091</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7168,39 +7168,39 @@
         <v>36.38</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>39.27</v>
+        <v>39.56</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>42.53</v>
+        <v>42.82</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>44.59</v>
+        <v>46.69</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>47.83</v>
+        <v>50.46</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>51.05</v>
+        <v>54.3</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>54.49</v>
+        <v>58.24</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>56.66</v>
+        <v>62.9</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>59.92</v>
+        <v>67.45</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>63.12</v>
+        <v>71.77</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7475,42 +7475,42 @@
         <v/>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.049989</v>
+        <v>0.050005</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.049986</v>
+        <v>0.049995</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.049977</v>
+        <v>0.049997</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.050008</v>
+        <v>0.049993</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.049989</v>
+        <v>0.050011</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.049994</v>
+        <v>0.049991</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050024</v>
+        <v>0.049993</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.05</v>
+        <v>0.049997</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.05</v>
+        <v>0.050002</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.050009</v>
+        <v>0.050011</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -8014,16 +8014,16 @@
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8142,16 +8142,16 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8378,36 +8378,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.087099</v>
+        <v>0.09588099999999999</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.09035899999999999</v>
+        <v>0.089674</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.052618</v>
+        <v>0.097723</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.07834099999999999</v>
+        <v>0.08678900000000001</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.072029</v>
+        <v>0.08136699999999999</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.07212</v>
+        <v>0.0771</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.042235</v>
+        <v>0.084755</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.060968</v>
+        <v>0.076219</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.056478</v>
+        <v>0.06736200000000001</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.056597</v>
+        <v>0.06464200000000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8506,36 +8506,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.076169</v>
+        <v>0.083846</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.079819</v>
+        <v>0.079291</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.046938</v>
+        <v>0.087239</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.07026</v>
+        <v>0.078227</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.065086</v>
+        <v>0.073921</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065593</v>
+        <v>0.07052899999999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.038647</v>
+        <v>0.07800799999999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.055983</v>
+        <v>0.070589</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.052107</v>
+        <v>0.06271699999999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.05243</v>
+        <v>0.060445</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9158,36 +9158,36 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.662235</v>
+        <v>-0.666805</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.228587</v>
+        <v>-0.245829</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.07037</v>
+        <v>-0.211728</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>0.108147</v>
+        <v>-0.098774</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.837638</v>
+        <v>0.488778</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.059841</v>
+        <v>-0.158555</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.031873</v>
+        <v>-0.150352</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.0527</v>
+        <v>-0.1712</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.024096</v>
+        <v>-0.156616</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.003401</v>
+        <v>-0.141104</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9277,36 +9277,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>-0.555219</v>
+        <v>-0.556732</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.540362</v>
+        <v>-0.54201</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.5360819999999999</v>
+        <v>-0.549828</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.502901</v>
+        <v>-0.520309</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.163265</v>
+        <v>-0.197952</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.157706</v>
+        <v>-0.197842</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.155556</v>
+        <v>-0.194656</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.14786</v>
+        <v>-0.193548</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.146341</v>
+        <v>-0.187234</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.140426</v>
+        <v>-0.183857</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9578,42 +9578,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.180909</v>
+        <v>0.180907</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.180906</v>
+        <v>0.180908</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180906</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.180911</v>
+        <v>0.180906</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.180907</v>
+        <v>0.18091</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.18091</v>
+        <v>0.180905</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.180911</v>
+        <v>0.180907</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180907</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.180908</v>
+        <v>0.180909</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.180904</v>
+        <v>0.18091</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -10108,7 +10108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO98"/>
+  <dimension ref="A1:AO106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16805,78 +16805,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>11206.18</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-13219.11</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-2539.17</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>4691.48</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-9364.360000000001</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-20431.16</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>3447.57</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-6456.83</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>7608.5</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>31774.82</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>36374.06</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>2027.83</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>31264.96</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>1021.58</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>67122.2</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>101436.57</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>16512.52</v>
-      </c>
-      <c r="W82" s="18" t="n">
-        <v>-70061.75</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>131093.02</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>103058.03</v>
-      </c>
-      <c r="Z82" s="34" t="n">
-        <v>180601.82</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
       <c r="AA82" s="18" t="n">
-        <v>34757.24</v>
+        <v>2584.6</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>65537.32000000001</v>
+        <v>2977.15</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16898,78 +16839,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>0</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>30.76</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>74.15000000000001</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>-16.65</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>-196.96</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="U83" s="34" t="n">
-        <v>175.77</v>
-      </c>
-      <c r="V83" s="18" t="n">
-        <v>-89.88</v>
-      </c>
-      <c r="W83" s="18" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>-2832.46</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>-539.27</v>
-      </c>
-      <c r="Z83" s="34" t="n">
-        <v>-3461.13</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
+      <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="18" t="n">
-        <v>-669.98</v>
+        <v>70.67</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>-545.96</v>
+        <v>153.84</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16991,78 +16873,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>25662.75</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>19784.47</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>-255.51</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>35226.79</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>-6669.38</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>48086.37</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>-3427.61</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>1568.59</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>7435.93</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>-19063.26</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>-13486.35</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>-5871.12</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>-11540.7</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>11146.62</v>
-      </c>
-      <c r="T84" s="18" t="n">
-        <v>-17858.43</v>
-      </c>
-      <c r="U84" s="34" t="n">
-        <v>-24123.63</v>
-      </c>
-      <c r="V84" s="18" t="n">
-        <v>13441.99</v>
-      </c>
-      <c r="W84" s="18" t="n">
-        <v>4711.28</v>
-      </c>
-      <c r="X84" s="18" t="n">
-        <v>-61778.72</v>
-      </c>
-      <c r="Y84" s="18" t="n">
-        <v>-101387.65</v>
-      </c>
-      <c r="Z84" s="34" t="n">
-        <v>-145013.1</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
+      <c r="Z84" s="9" t="n"/>
       <c r="AA84" s="18" t="n">
-        <v>66951.05</v>
+        <v>6533.76</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>79379.03</v>
+        <v>3974.81</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17084,78 +16907,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>57.42</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>2811.43</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>295.87</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>3871.03</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>2529.87</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>9508.200000000001</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>1982.57</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>880.47</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>1773.95</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>748.45</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>5385.44</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>422.92</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>390.16</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>1275.05</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>5721.99</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>7810.12</v>
-      </c>
-      <c r="V85" s="18" t="n">
-        <v>3729.41</v>
-      </c>
-      <c r="W85" s="18" t="n">
-        <v>1701.46</v>
-      </c>
-      <c r="X85" s="18" t="n">
-        <v>1520.21</v>
-      </c>
-      <c r="Y85" s="18" t="n">
-        <v>6141.6</v>
-      </c>
-      <c r="Z85" s="34" t="n">
-        <v>13092.68</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="Z85" s="9" t="n"/>
       <c r="AA85" s="18" t="n">
-        <v>2940.67</v>
+        <v>3025.36</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>5544.41</v>
+        <v>1853.97</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17177,78 +16941,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>781.0599999999999</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>2964.4</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>601.3099999999999</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>4058.18</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>2642.65</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>10266.54</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>2067.57</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>880.47</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>1773.95</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>787.25</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>5509.24</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>422.92</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>430.16</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>1292.95</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>6104.24</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>8250.27</v>
-      </c>
-      <c r="V86" s="18" t="n">
-        <v>3756.86</v>
-      </c>
-      <c r="W86" s="18" t="n">
-        <v>1812.97</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>1781.34</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>6448.1</v>
-      </c>
-      <c r="Z86" s="34" t="n">
-        <v>13799.27</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
       <c r="AA86" s="18" t="n">
-        <v>3056.27</v>
+        <v>925.1</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>6350.91</v>
+        <v>0</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17270,78 +16975,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>723.64</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>152.97</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>305.44</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>187.15</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>112.78</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>758.34</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>85</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>123.8</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>382.25</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>440.15</v>
-      </c>
-      <c r="V87" s="18" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="W87" s="18" t="n">
-        <v>111.51</v>
-      </c>
-      <c r="X87" s="18" t="n">
-        <v>261.13</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>306.5</v>
-      </c>
-      <c r="Z87" s="34" t="n">
-        <v>706.59</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
+      <c r="Z87" s="9" t="n"/>
       <c r="AA87" s="18" t="n">
-        <v>115.6</v>
+        <v>382.43</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>806.5</v>
+        <v>662.71</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -17363,33 +17009,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>763.9</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="I88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="K88" s="9" t="n"/>
-      <c r="O88" s="18" t="n">
-        <v>0.22</v>
-      </c>
       <c r="P88" s="9" t="n"/>
-      <c r="S88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="U88" s="9" t="n"/>
       <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+      <c r="AA88" s="18" t="n">
+        <v>4813.46</v>
+      </c>
+      <c r="AB88" s="19" t="n">
+        <v>31.88</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -17410,78 +17043,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>-31391.76</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>-35715.93</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>-3562.47</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>1512.55</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>-21244</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>-59009.85</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>-1626.27</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>-4229.73</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>-11243.64</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>-1477.53</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>-18577.17</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>-2546.71</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>-748.78</v>
-      </c>
-      <c r="S89" s="18" t="n">
-        <v>-44413.78</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>-3678.25</v>
-      </c>
-      <c r="U89" s="34" t="n">
-        <v>-51387.52</v>
-      </c>
-      <c r="V89" s="18" t="n">
-        <v>-299.2</v>
-      </c>
-      <c r="W89" s="18" t="n">
-        <v>-262.19</v>
-      </c>
-      <c r="X89" s="18" t="n">
-        <v>-254.22</v>
-      </c>
-      <c r="Y89" s="18" t="n">
-        <v>-255.06</v>
-      </c>
-      <c r="Z89" s="34" t="n">
-        <v>-1070.67</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="U89" s="9" t="n"/>
+      <c r="Z89" s="9" t="n"/>
       <c r="AA89" s="18" t="n">
-        <v>-269.42</v>
+        <v>2513.93</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>-291.69</v>
+        <v>2823.31</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17503,38 +17077,79 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>28800</v>
+        <v>11206.18</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>25970</v>
+        <v>-13219.11</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>1000</v>
+        <v>-2539.17</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>4691.48</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>21400</v>
+        <v>-9364.360000000001</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>48370</v>
+        <v>-20431.16</v>
+      </c>
+      <c r="L90" s="18" t="n">
+        <v>3447.57</v>
+      </c>
+      <c r="M90" s="18" t="n">
+        <v>-6456.83</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>4600</v>
+        <v>7608.5</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="9" t="n"/>
-      <c r="U90" s="9" t="n"/>
-      <c r="Z90" s="9" t="n"/>
-      <c r="AB90" s="5" t="n"/>
+        <v>31774.82</v>
+      </c>
+      <c r="P90" s="34" t="n">
+        <v>36374.06</v>
+      </c>
+      <c r="Q90" s="18" t="n">
+        <v>2027.83</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>31264.96</v>
+      </c>
+      <c r="S90" s="18" t="n">
+        <v>1021.58</v>
+      </c>
+      <c r="T90" s="18" t="n">
+        <v>67122.2</v>
+      </c>
+      <c r="U90" s="34" t="n">
+        <v>101436.57</v>
+      </c>
+      <c r="V90" s="18" t="n">
+        <v>16512.52</v>
+      </c>
+      <c r="W90" s="18" t="n">
+        <v>-70061.75</v>
+      </c>
+      <c r="X90" s="18" t="n">
+        <v>131093.02</v>
+      </c>
+      <c r="Y90" s="18" t="n">
+        <v>103058.03</v>
+      </c>
+      <c r="Z90" s="34" t="n">
+        <v>180601.82</v>
+      </c>
+      <c r="AA90" s="18" t="n">
+        <v>34757.24</v>
+      </c>
+      <c r="AB90" s="19" t="n">
+        <v>65537.32000000001</v>
+      </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
       <c r="AE90" s="11" t="n"/>
@@ -17555,47 +17170,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>474.95</v>
+        <v>0</v>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>33.57</v>
+      </c>
       <c r="I91" s="18" t="n">
-        <v>69757.50999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>4279.62</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
+        <v>-0.36</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>30.76</v>
+      </c>
       <c r="L91" s="18" t="n">
-        <v>911.05</v>
+        <v>-5.63</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>81546.83</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>1625.03</v>
+        <v>-16.65</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>1292.67</v>
+        <v>4.17</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>85375.58</v>
+        <v>56.04</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>564.34</v>
+        <v>0</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1747.97</v>
+        <v>374.5</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>275.59</v>
-      </c>
-      <c r="U91" s="9" t="n"/>
-      <c r="Z91" s="9" t="n"/>
-      <c r="AB91" s="5" t="n"/>
+        <v>-196.96</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>175.77</v>
+      </c>
+      <c r="V91" s="18" t="n">
+        <v>-89.88</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>-2832.46</v>
+      </c>
+      <c r="Y91" s="18" t="n">
+        <v>-539.27</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>-3461.13</v>
+      </c>
+      <c r="AA91" s="18" t="n">
+        <v>-669.98</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>-545.96</v>
+      </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -17616,60 +17263,79 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>424.69</v>
+        <v>25662.75</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>426.12</v>
+        <v>19784.47</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>982.1</v>
+        <v>-255.51</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>66533.39999999999</v>
+        <v>35226.79</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>3698.02</v>
+        <v>-6669.38</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>71639.64</v>
+        <v>48086.37</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>904.13</v>
+        <v>-3427.61</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>71127.87</v>
+        <v>1568.59</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>5755.28</v>
+        <v>7435.93</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>1139.27</v>
+        <v>-19063.26</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>78926.55</v>
+        <v>-13486.35</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>1524.92</v>
+        <v>-5871.12</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>890.4</v>
+        <v>-11540.7</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>85725.39999999999</v>
+        <v>11146.62</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>1815.85</v>
+        <v>-17858.43</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>89956.57000000001</v>
-      </c>
-      <c r="Z92" s="9" t="n"/>
-      <c r="AB92" s="5" t="n"/>
+        <v>-24123.63</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>13441.99</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>4711.28</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>-61778.72</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>-101387.65</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>-145013.1</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>66951.05</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>79379.03</v>
+      </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -17690,78 +17356,78 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>-1929.34</v>
+        <v>57.42</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>-8555.57</v>
+        <v>2811.43</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>-1001.15</v>
+        <v>295.87</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>-1074.74</v>
+        <v>3871.03</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>-1112.96</v>
+        <v>2529.87</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>-11744.42</v>
+        <v>9508.200000000001</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>-1259.34</v>
+        <v>1982.57</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>-3268.31</v>
+        <v>880.47</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>-2145.07</v>
+        <v>1773.95</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>-1240.93</v>
+        <v>748.45</v>
       </c>
       <c r="P93" s="34" t="n">
-        <v>-7913.65</v>
+        <v>5385.44</v>
       </c>
       <c r="Q93" s="18" t="n">
-        <v>-1221.78</v>
+        <v>422.92</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>-1261.82</v>
+        <v>390.16</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>-895.71</v>
+        <v>1275.05</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>-1533.68</v>
+        <v>5721.99</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>-4912.99</v>
+        <v>7810.12</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>-33.52</v>
+        <v>3729.41</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>-30.71</v>
+        <v>1701.46</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>-32.41</v>
+        <v>1520.21</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>-31.05</v>
+        <v>6141.6</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>-127.69</v>
+        <v>13092.68</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>-70.67</v>
+        <v>2940.67</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>-153.84</v>
+        <v>5544.41</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -17783,77 +17449,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>5474.11</v>
+        <v>781.0599999999999</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>-29149.67</v>
+        <v>2964.4</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>-6351.87</v>
+        <v>601.3099999999999</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>41610.02</v>
+        <v>4058.18</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>-37565.86</v>
+        <v>2642.65</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>-31457.38</v>
+        <v>10266.54</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>-1563.74</v>
+        <v>2067.57</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>-9132.99</v>
+        <v>880.47</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>3907.25</v>
+        <v>1773.95</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>11028.66</v>
+        <v>787.25</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>4239.18</v>
+        <v>5509.24</v>
       </c>
       <c r="Q94" s="18" t="n">
-        <v>-6338.16</v>
+        <v>422.92</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>18957.39</v>
+        <v>430.16</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>-32279.48</v>
+        <v>1292.95</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>45521.62</v>
+        <v>6104.24</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>25861.37</v>
+        <v>8250.27</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>29655.38</v>
+        <v>3756.86</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>41485.32</v>
+        <v>1812.97</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>-38037.81</v>
+        <v>1781.34</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>1416.37</v>
+        <v>6448.1</v>
       </c>
       <c r="Z94" s="34" t="n">
-        <v>34519.26</v>
+        <v>13799.27</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>101438.88</v>
-      </c>
-      <c r="AB94" s="5" t="n"/>
+        <v>3056.27</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>6350.91</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -17874,78 +17542,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>5474.1</v>
+        <v>723.64</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="18" t="n">
-        <v>31964.13</v>
+        <v>152.97</v>
       </c>
       <c r="H95" s="18" t="n">
-        <v>-6351.87</v>
+        <v>305.44</v>
       </c>
       <c r="I95" s="18" t="n">
-        <v>41610.02</v>
+        <v>187.15</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>-37565.86</v>
+        <v>112.78</v>
       </c>
       <c r="K95" s="34" t="n">
-        <v>29656.42</v>
+        <v>758.34</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>28092.68</v>
+        <v>85</v>
       </c>
       <c r="M95" s="18" t="n">
-        <v>-9132.99</v>
+        <v>0</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>3907.25</v>
+        <v>0</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>11028.66</v>
+        <v>38.8</v>
       </c>
       <c r="P95" s="34" t="n">
-        <v>33895.6</v>
+        <v>123.8</v>
       </c>
       <c r="Q95" s="18" t="n">
-        <v>27557.44</v>
+        <v>0</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>18957.39</v>
+        <v>40</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>-32279.48</v>
+        <v>17.9</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>45521.62</v>
+        <v>382.25</v>
       </c>
       <c r="U95" s="34" t="n">
-        <v>59756.97</v>
+        <v>440.15</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>89412.35000000001</v>
+        <v>27.45</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>41485.32</v>
+        <v>111.51</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>-38037.81</v>
+        <v>261.13</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>1416.37</v>
+        <v>306.5</v>
       </c>
       <c r="Z95" s="34" t="n">
-        <v>94276.23</v>
+        <v>706.59</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>195715.11</v>
+        <v>115.6</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>144624.65</v>
+        <v>806.5</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -17967,71 +17635,33 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>763.9</v>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="G96" s="18" t="n">
-        <v>452.52</v>
-      </c>
-      <c r="H96" s="18" t="n">
+      <c r="I96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="18" t="n">
-        <v>555.98</v>
-      </c>
       <c r="J96" s="18" t="n">
-        <v>1712.89</v>
-      </c>
-      <c r="K96" s="34" t="n">
-        <v>2721.39</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>464.6</v>
-      </c>
-      <c r="M96" s="18" t="n">
-        <v>1688.71</v>
-      </c>
-      <c r="N96" s="18" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K96" s="9" t="n"/>
       <c r="O96" s="18" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="P96" s="34" t="n">
-        <v>2164.68</v>
-      </c>
-      <c r="Q96" s="18" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="R96" s="18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P96" s="9" t="n"/>
+      <c r="S96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="18" t="n">
-        <v>3054.29</v>
+      <c r="T96" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="U96" s="9" t="n"/>
-      <c r="V96" s="18" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="W96" s="18" t="n">
-        <v>43.97</v>
-      </c>
-      <c r="X96" s="18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Y96" s="18" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="Z96" s="34" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="AA96" s="18" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="AB96" s="19" t="n">
-        <v>15</v>
-      </c>
+      <c r="Z96" s="9" t="n"/>
+      <c r="AB96" s="5" t="n"/>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
       <c r="AE96" s="11" t="n"/>
@@ -18052,25 +17682,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>-31391.76</v>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>-35715.93</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>-3562.47</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>1512.55</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>-21244</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>-59009.85</v>
+      </c>
       <c r="L97" s="18" t="n">
-        <v>362.54</v>
+        <v>-1626.27</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>357.65</v>
-      </c>
-      <c r="P97" s="9" t="n"/>
-      <c r="U97" s="9" t="n"/>
-      <c r="Z97" s="9" t="n"/>
+        <v>-4229.73</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>-11243.64</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>-1477.53</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>-18577.17</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>-2546.71</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>-748.78</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>-44413.78</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>-3678.25</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>-51387.52</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>-299.2</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>-262.19</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>-254.22</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>-255.06</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>-1070.67</v>
+      </c>
       <c r="AA97" s="18" t="n">
-        <v>198.75</v>
+        <v>-269.42</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>137.85</v>
+        <v>-291.69</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -18092,51 +17775,38 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>28800</v>
       </c>
       <c r="F98" s="9" t="n"/>
-      <c r="K98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>25970</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>21400</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>48370</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>4600</v>
+      </c>
       <c r="O98" s="18" t="n">
-        <v>315.42</v>
+        <v>0</v>
       </c>
       <c r="P98" s="9" t="n"/>
-      <c r="Q98" s="18" t="n">
-        <v>375.15</v>
-      </c>
-      <c r="R98" s="18" t="n">
-        <v>612.4400000000001</v>
-      </c>
-      <c r="S98" s="18" t="n">
-        <v>1172.98</v>
-      </c>
-      <c r="T98" s="18" t="n">
-        <v>2406.24</v>
-      </c>
-      <c r="U98" s="34" t="n">
-        <v>4566.81</v>
-      </c>
-      <c r="V98" s="18" t="n">
-        <v>850.29</v>
-      </c>
-      <c r="W98" s="18" t="n">
-        <v>1427.17</v>
-      </c>
-      <c r="X98" s="18" t="n">
-        <v>1629.68</v>
-      </c>
-      <c r="Y98" s="18" t="n">
-        <v>1289.75</v>
-      </c>
-      <c r="Z98" s="34" t="n">
-        <v>5196.89</v>
-      </c>
-      <c r="AA98" s="18" t="n">
-        <v>1962.58</v>
-      </c>
-      <c r="AB98" s="19" t="n">
-        <v>3358.96</v>
-      </c>
+      <c r="U98" s="9" t="n"/>
+      <c r="Z98" s="9" t="n"/>
+      <c r="AB98" s="5" t="n"/>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -18150,6 +17820,608 @@
       <c r="AM98" s="10" t="n"/>
       <c r="AN98" s="10" t="n"/>
       <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>474.95</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="I99" s="18" t="n">
+        <v>69757.50999999999</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>4279.62</v>
+      </c>
+      <c r="K99" s="9" t="n"/>
+      <c r="L99" s="18" t="n">
+        <v>911.05</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>81546.83</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>1292.67</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>85375.58</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>564.34</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>1747.97</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AB99" s="5" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>424.69</v>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>426.12</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>982.1</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>66533.39999999999</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>3698.02</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>71639.64</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>904.13</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>71127.87</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>5755.28</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>1139.27</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>78926.55</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>1524.92</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>890.4</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>85725.39999999999</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>1815.85</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>89956.57000000001</v>
+      </c>
+      <c r="Z100" s="9" t="n"/>
+      <c r="AB100" s="5" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>-1929.34</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>-8555.57</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>-1001.15</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>-1074.74</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>-1112.96</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>-11744.42</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>-1259.34</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>-3268.31</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>-2145.07</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>-1240.93</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>-7913.65</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>-1221.78</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>-1261.82</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>-895.71</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>-1533.68</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>-4912.99</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>-33.52</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>-30.71</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>-32.41</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>-31.05</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>-127.69</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>-70.67</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>-153.84</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>5474.11</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>-29149.67</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>-6351.87</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>41610.02</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>-37565.86</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>-31457.38</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>-1563.74</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>-9132.99</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>3907.25</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>11028.66</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>4239.18</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>-6338.16</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>18957.39</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>-32279.48</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>45521.62</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>25861.37</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>29655.38</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>41485.32</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>-38037.81</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>1416.37</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>34519.26</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>101438.88</v>
+      </c>
+      <c r="AB102" s="5" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>5474.1</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>31964.13</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>-6351.87</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>41610.02</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>-37565.86</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>29656.42</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>28092.68</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>-9132.99</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>3907.25</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>11028.66</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>33895.6</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>27557.44</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>18957.39</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>-32279.48</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>45521.62</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>59756.97</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>89412.35000000001</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>41485.32</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>-38037.81</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>1416.37</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>94276.23</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>195715.11</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>144624.65</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>452.52</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>555.98</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>1712.89</v>
+      </c>
+      <c r="K104" s="34" t="n">
+        <v>2721.39</v>
+      </c>
+      <c r="L104" s="18" t="n">
+        <v>464.6</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>1688.71</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="P104" s="34" t="n">
+        <v>2164.68</v>
+      </c>
+      <c r="Q104" s="18" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="R104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>3054.29</v>
+      </c>
+      <c r="U104" s="9" t="n"/>
+      <c r="V104" s="18" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="W104" s="18" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="X104" s="18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="Z104" s="34" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="AA104" s="18" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="L105" s="18" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="P105" s="9" t="n"/>
+      <c r="U105" s="9" t="n"/>
+      <c r="Z105" s="9" t="n"/>
+      <c r="AA105" s="18" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>137.85</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="O106" s="18" t="n">
+        <v>315.42</v>
+      </c>
+      <c r="P106" s="9" t="n"/>
+      <c r="Q106" s="18" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>612.4400000000001</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>1172.98</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>2406.24</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>4566.81</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>850.29</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>1427.17</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>1629.68</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>1289.75</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>5196.89</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>1962.58</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>3358.96</v>
+      </c>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18410,7 +18682,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39289,7 +39561,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3097.4</v>
+        <v>3807.4</v>
       </c>
     </row>
     <row r="30">
@@ -39309,7 +39581,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.37</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="32">
@@ -39329,7 +39601,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2013</v>
+        <v>0.2474</v>
       </c>
     </row>
     <row r="34">
@@ -39339,7 +39611,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="35">
@@ -39349,7 +39621,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34500</v>
+        <v>42300</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4469,7 +4469,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5340,35 +5340,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5459,35 +5459,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5578,35 +5578,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5697,35 +5697,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5816,35 +5816,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5935,35 +5935,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6054,35 +6054,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6173,35 +6173,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6308,7 +6308,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>49050</v>
+        <v>47500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6399,7 +6399,7 @@
         <v>70000</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>49200</v>
+        <v>49400</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6490,7 +6490,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>47400</v>
+        <v>47050</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6581,7 +6581,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>48725</v>
+        <v>48316.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>49050</v>
+        <v>47500</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05928745488891241</v>
+        <v>0.05928745488891243</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05214443690966399</v>
+        <v>0.05214443690966394</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.01681726185905052</v>
+        <v>0.01681726185905281</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39165,7 +39165,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41393,7 +41393,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.99</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="32">
@@ -41403,7 +41403,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4469,7 +4469,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5340,35 +5340,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5459,35 +5459,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5578,35 +5578,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5697,35 +5697,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5816,35 +5816,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5935,35 +5935,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6054,35 +6054,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6173,35 +6173,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6308,7 +6308,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>47500</v>
+        <v>45000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6490,7 +6490,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>47050</v>
+        <v>44800</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6581,7 +6581,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>48316.7</v>
+        <v>47537.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9717,11 +9717,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>47500</v>
+        <v>45000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 48,200원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 49,100원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39165,7 +39165,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41393,7 +41393,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.58</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="32">
@@ -41403,7 +41403,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4469,7 +4469,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -5340,35 +5340,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5459,35 +5459,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5578,35 +5578,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5697,35 +5697,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5816,35 +5816,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5935,35 +5935,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6054,35 +6054,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6173,35 +6173,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6308,7 +6308,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>45000</v>
+        <v>42850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6490,7 +6490,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>44800</v>
+        <v>42550</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6581,7 +6581,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>47537.5</v>
+        <v>46560</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9717,11 +9717,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>45000</v>
+        <v>42850</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 49,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,100원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39165,7 +39165,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41393,7 +41393,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.92</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="32">
@@ -41403,7 +41403,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1674,79 +1674,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI42" authorId="0" shapeId="0">
+    <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN42" authorId="0" shapeId="0">
+    <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -3467,159 +3407,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="Y34" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 1121억 − (비영업손익 750억 − 12분기 기준선 16억) × (1 − 8.0%, 모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)) × 지배 비중 1.00(그 분기 지배NI/NI) = 446억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 3,304.4원</t>
-      </text>
-    </comment>
-    <comment ref="AA34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AB34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 734억 × (1 − 세율 8.1% [모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = 446억 ÷ 유통주식수 · 초과 = 비영업손익 750억 − 12분기 기준선 16억 · 보고 EPS 3,304원(EPS 행 불변) · 상수 674.95·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
@@ -4453,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4469,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4357,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4632,50 +4482,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2025Q4 보고 3,304→조정 1,315원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 9.3/11.2/16.2배(hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/071970.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/071970.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 24.9% &gt; 추세 12.9% × 1.10 (suppliers_mentions·시차 1·4분기 이동합·창 19, r=0.99 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 750억(영업이익 279억의 3배, 12분기 중위 34억·기준선 16억) → 지배NI 1,121억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 1,314.7원(보고 3,304.4원; 초과 비영업손익 734억 × (1 − 세율 8.1%) × 지배 비중 1.00 = 675억 차감 — 추정, 조정EPS 행)</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 24.9% &gt; 추세 12.9% × 1.10 (suppliers_mentions·시차 1·4분기 이동합·창 19, r=0.99 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 750억(영업이익 279억의 3배, 12분기 중위 34억·기준선 16억) → 지배NI 1,121억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 1,314.7원(보고 3,304.4원; 초과 비영업손익 734억 × (1 − 세율 8.1%) × 지배 비중 1.00 = 675억 차감 — 추정, 조정EPS 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 24.9, "op_wape_pct": 66.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 18.0, "wape_trend": 25.4, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 971.04, "rev_act": 1091.69, "op_pred": 101.46, "op_act": 202.88}, {"q": "2025Q4", "rev_pred": 1043.01, "rev_act": 1109.76, "op_pred": 108.98, "op_act": 278.89}, {"q": "2026Q1", "rev_pred": 488.89, "rev_act": 1334.61, "op_pred": 51.08, "op_act": 325.64}, {"q": "2026Q2", "rev_pred": 1114.04, "rev_act": 1281.19, "op_pred": 116.4, "op_act": 312.86}]}</t>
         </is>
@@ -4692,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO60"/>
+  <dimension ref="A1:AO59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6879,11 +6736,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6891,19 +6748,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6911,19 +6768,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -7819,11 +7676,11 @@
         <v/>
       </c>
       <c r="AC28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AD28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AE28" s="25">
@@ -7831,19 +7688,19 @@
         <v/>
       </c>
       <c r="AF28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AG28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AH28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AI28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AJ28" s="25">
@@ -7851,19 +7708,19 @@
         <v/>
       </c>
       <c r="AK28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AL28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AM28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AN28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AO28" s="25">
@@ -7984,11 +7841,11 @@
         <v/>
       </c>
       <c r="AC29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AD29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AE29" s="25">
@@ -7996,19 +7853,19 @@
         <v/>
       </c>
       <c r="AF29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AG29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AH29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AI29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AJ29" s="25">
@@ -8016,19 +7873,19 @@
         <v/>
       </c>
       <c r="AK29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AL29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AM29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AN29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AO29" s="25">
@@ -9396,264 +9253,176 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21">
-        <f>IFERROR(subQ!J34/subQ!E34-1,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="21">
-        <f>IFERROR(subQ!L34/subQ!G34-1,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="21">
-        <f>IFERROR(subQ!M34/subQ!H34-1,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="21">
-        <f>IFERROR(subQ!N34/subQ!I34-1,"")</f>
-        <v/>
-      </c>
-      <c r="O41" s="21">
-        <f>IFERROR(subQ!O34/subQ!J34-1,"")</f>
-        <v/>
-      </c>
-      <c r="P41" s="22" t="n"/>
-      <c r="Q41" s="21">
-        <f>IFERROR(subQ!Q34/subQ!L34-1,"")</f>
-        <v/>
-      </c>
-      <c r="R41" s="21">
-        <f>IFERROR(subQ!R34/subQ!M34-1,"")</f>
-        <v/>
-      </c>
-      <c r="S41" s="21">
-        <f>IFERROR(subQ!S34/subQ!N34-1,"")</f>
-        <v/>
-      </c>
-      <c r="T41" s="21">
-        <f>IFERROR(subQ!T34/subQ!O34-1,"")</f>
-        <v/>
-      </c>
-      <c r="U41" s="22" t="n"/>
-      <c r="V41" s="21">
-        <f>IFERROR(subQ!V34/subQ!Q34-1,"")</f>
-        <v/>
-      </c>
-      <c r="W41" s="21">
-        <f>IFERROR(subQ!W34/subQ!R34-1,"")</f>
-        <v/>
-      </c>
-      <c r="X41" s="21">
-        <f>IFERROR(subQ!X34/subQ!S34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y41" s="21">
-        <f>IFERROR(subQ!Y34/subQ!T34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z41" s="22" t="n"/>
-      <c r="AA41" s="21">
-        <f>IFERROR(subQ!AA34/subQ!V34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB41" s="23">
-        <f>IFERROR(subQ!AB34/subQ!W34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC41" s="24" t="n">
-        <v>0.27992191</v>
-      </c>
-      <c r="AD41" s="24" t="n">
-        <v>-0.334753176</v>
-      </c>
-      <c r="AE41" s="25" t="n"/>
-      <c r="AF41" s="24" t="n">
-        <v>0.248734635</v>
-      </c>
-      <c r="AG41" s="24" t="n">
-        <v>0.077799063</v>
-      </c>
-      <c r="AH41" s="24" t="n">
-        <v>0.212366538</v>
-      </c>
-      <c r="AI41" s="24" t="n">
-        <v>0.211982621</v>
-      </c>
-      <c r="AJ41" s="25" t="n"/>
-      <c r="AK41" s="24" t="n">
-        <v>0.208067941</v>
-      </c>
-      <c r="AL41" s="24" t="n">
-        <v>0.208847635</v>
-      </c>
-      <c r="AM41" s="24" t="n">
-        <v>0.13084293</v>
-      </c>
-      <c r="AN41" s="24" t="n">
-        <v>0.130377358</v>
-      </c>
-      <c r="AO41" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E41" s="27">
+        <f>subQ!E36</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>subQ!F36</f>
+        <v/>
+      </c>
+      <c r="G41" s="27">
+        <f>subQ!G36</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>subQ!H36</f>
+        <v/>
+      </c>
+      <c r="I41" s="27">
+        <f>subQ!I36</f>
+        <v/>
+      </c>
+      <c r="J41" s="27">
+        <f>subQ!J36</f>
+        <v/>
+      </c>
+      <c r="K41" s="28">
+        <f>subQ!K36</f>
+        <v/>
+      </c>
+      <c r="L41" s="27">
+        <f>subQ!L36</f>
+        <v/>
+      </c>
+      <c r="M41" s="27">
+        <f>subQ!M36</f>
+        <v/>
+      </c>
+      <c r="N41" s="27">
+        <f>subQ!N36</f>
+        <v/>
+      </c>
+      <c r="O41" s="27">
+        <f>subQ!O36</f>
+        <v/>
+      </c>
+      <c r="P41" s="28">
+        <f>subQ!P36</f>
+        <v/>
+      </c>
+      <c r="Q41" s="27">
+        <f>subQ!Q36</f>
+        <v/>
+      </c>
+      <c r="R41" s="27">
+        <f>subQ!R36</f>
+        <v/>
+      </c>
+      <c r="S41" s="27">
+        <f>subQ!S36</f>
+        <v/>
+      </c>
+      <c r="T41" s="27">
+        <f>subQ!T36</f>
+        <v/>
+      </c>
+      <c r="U41" s="28">
+        <f>subQ!U36</f>
+        <v/>
+      </c>
+      <c r="V41" s="27">
+        <f>subQ!V36</f>
+        <v/>
+      </c>
+      <c r="W41" s="27">
+        <f>subQ!W36</f>
+        <v/>
+      </c>
+      <c r="X41" s="27">
+        <f>subQ!X36</f>
+        <v/>
+      </c>
+      <c r="Y41" s="27">
+        <f>subQ!Y36</f>
+        <v/>
+      </c>
+      <c r="Z41" s="28">
+        <f>subQ!Z36</f>
+        <v/>
+      </c>
+      <c r="AA41" s="27">
+        <f>subQ!AA36</f>
+        <v/>
+      </c>
+      <c r="AB41" s="29">
+        <f>subQ!AB36</f>
+        <v/>
+      </c>
+      <c r="AC41" s="32" t="n"/>
+      <c r="AD41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="31">
+        <f>subQ!AE36</f>
+        <v/>
+      </c>
+      <c r="AF41" s="32" t="n"/>
+      <c r="AG41" s="32" t="n"/>
+      <c r="AH41" s="32" t="n"/>
+      <c r="AI41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="31">
+        <f>subQ!AJ36</f>
+        <v/>
+      </c>
+      <c r="AK41" s="32" t="n"/>
+      <c r="AL41" s="32" t="n"/>
+      <c r="AM41" s="32" t="n"/>
+      <c r="AN41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" s="31">
+        <f>subQ!AO36</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E42" s="27">
-        <f>subQ!E36</f>
-        <v/>
-      </c>
-      <c r="F42" s="28">
-        <f>subQ!F36</f>
-        <v/>
-      </c>
-      <c r="G42" s="27">
-        <f>subQ!G36</f>
-        <v/>
-      </c>
-      <c r="H42" s="27">
-        <f>subQ!H36</f>
-        <v/>
-      </c>
-      <c r="I42" s="27">
-        <f>subQ!I36</f>
-        <v/>
-      </c>
-      <c r="J42" s="27">
-        <f>subQ!J36</f>
-        <v/>
-      </c>
-      <c r="K42" s="28">
-        <f>subQ!K36</f>
-        <v/>
-      </c>
-      <c r="L42" s="27">
-        <f>subQ!L36</f>
-        <v/>
-      </c>
-      <c r="M42" s="27">
-        <f>subQ!M36</f>
-        <v/>
-      </c>
-      <c r="N42" s="27">
-        <f>subQ!N36</f>
-        <v/>
-      </c>
-      <c r="O42" s="27">
-        <f>subQ!O36</f>
-        <v/>
-      </c>
-      <c r="P42" s="28">
-        <f>subQ!P36</f>
-        <v/>
-      </c>
-      <c r="Q42" s="27">
-        <f>subQ!Q36</f>
-        <v/>
-      </c>
-      <c r="R42" s="27">
-        <f>subQ!R36</f>
-        <v/>
-      </c>
-      <c r="S42" s="27">
-        <f>subQ!S36</f>
-        <v/>
-      </c>
-      <c r="T42" s="27">
-        <f>subQ!T36</f>
-        <v/>
-      </c>
-      <c r="U42" s="28">
-        <f>subQ!U36</f>
-        <v/>
-      </c>
-      <c r="V42" s="27">
-        <f>subQ!V36</f>
-        <v/>
-      </c>
-      <c r="W42" s="27">
-        <f>subQ!W36</f>
-        <v/>
-      </c>
-      <c r="X42" s="27">
-        <f>subQ!X36</f>
-        <v/>
-      </c>
-      <c r="Y42" s="27">
-        <f>subQ!Y36</f>
-        <v/>
-      </c>
-      <c r="Z42" s="28">
-        <f>subQ!Z36</f>
-        <v/>
-      </c>
-      <c r="AA42" s="27">
-        <f>subQ!AA36</f>
-        <v/>
-      </c>
-      <c r="AB42" s="29">
-        <f>subQ!AB36</f>
-        <v/>
-      </c>
-      <c r="AC42" s="32" t="n"/>
-      <c r="AD42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="31">
-        <f>subQ!AE36</f>
-        <v/>
-      </c>
-      <c r="AF42" s="32" t="n"/>
-      <c r="AG42" s="32" t="n"/>
-      <c r="AH42" s="32" t="n"/>
-      <c r="AI42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="31">
-        <f>subQ!AJ36</f>
-        <v/>
-      </c>
-      <c r="AK42" s="32" t="n"/>
-      <c r="AL42" s="32" t="n"/>
-      <c r="AM42" s="32" t="n"/>
-      <c r="AN42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="31">
-        <f>subQ!AO36</f>
-        <v/>
-      </c>
+      <c r="F42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="10" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="11" t="n"/>
+      <c r="AK42" s="10" t="n"/>
+      <c r="AL42" s="10" t="n"/>
+      <c r="AM42" s="10" t="n"/>
+      <c r="AN42" s="10" t="n"/>
+      <c r="AO42" s="11" t="n"/>
     </row>
     <row r="43">
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
@@ -9675,14 +9444,22 @@
       <c r="AO43" s="11" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="n">
+        <v>42850</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,100원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9708,20 +9485,22 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D45" s="34" t="n">
-        <v>42850</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,100원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9747,22 +9526,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9788,20 +9565,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9827,20 +9604,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>9.300000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 16분기, 25/50/75 백분위)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9866,20 +9643,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D49" s="30" t="n">
-        <v>11.2</v>
+        <v>16.2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9905,20 +9682,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>16.2</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9944,20 +9721,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D51" s="36" t="n">
+        <v>0.08049720499330666</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0805) · 최근 12분기 유효세율 -22.1% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q3~2026Q2)의 법인세/세전 중위 8.0%</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9983,20 +9760,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08049720499330666</v>
+        <v>0.05928745488891241</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0805) · 최근 12분기 유효세율 -22.1% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q3~2026Q2)의 법인세/세전 중위 8.0%</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0593)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -10022,20 +9799,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.05928745488891243</v>
+        <v>1</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0593)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -10061,20 +9838,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>1</v>
+        <v>0.05214443690966399</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0521)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -10100,20 +9877,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05214443690966394</v>
+        <v>0.01681726185905052</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0521)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0168)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10139,20 +9916,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="n">
-        <v>0.01681726185905281</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0168)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10178,20 +9955,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10217,18 +9992,18 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -10254,15 +10029,15 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -10287,43 +10062,6 @@
       <c r="AM59" s="10" t="n"/>
       <c r="AN59" s="10" t="n"/>
       <c r="AO59" s="11" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="U60" s="9" t="n"/>
-      <c r="Z60" s="9" t="n"/>
-      <c r="AB60" s="5" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="11" t="n"/>
-      <c r="AF60" s="10" t="n"/>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="11" t="n"/>
-      <c r="AK60" s="10" t="n"/>
-      <c r="AL60" s="10" t="n"/>
-      <c r="AM60" s="10" t="n"/>
-      <c r="AN60" s="10" t="n"/>
-      <c r="AO60" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10585,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19173,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28675,11 +28413,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB28*변수!$D$55-AB26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AB28*변수!$D$54-AB26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC28*변수!$D$55-AC26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AC28*변수!$D$54-AC26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -28687,19 +28425,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD28*변수!$D$55-AD26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AD28*변수!$D$54-AD26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF28*변수!$D$55-AF26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AF28*변수!$D$54-AF26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG28*변수!$D$55-AG26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AG28*변수!$D$54-AG26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH28*변수!$D$55-AH26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AH28*변수!$D$54-AH26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -28707,19 +28445,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI28*변수!$D$55-AI26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AI28*변수!$D$54-AI26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK28*변수!$D$55-AK26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AK28*변수!$D$54-AK26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL28*변수!$D$55-AL26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AL28*변수!$D$54-AL26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM28*변수!$D$55-AM26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AM28*변수!$D$54-AM26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -32008,86 +31746,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E34" s="18" t="n">
-        <v>325.7</v>
+      <c r="E34" s="18">
+        <f>IFERROR(E33,"")</f>
+        <v/>
       </c>
       <c r="F34" s="37" t="n"/>
-      <c r="G34" s="18" t="n">
-        <v>-57.4</v>
-      </c>
-      <c r="H34" s="18" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I34" s="18" t="n">
-        <v>438.2</v>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>92.59999999999999</v>
+      <c r="G34" s="18">
+        <f>IFERROR(G33,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(H33,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(I33,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>IFERROR(J33,"")</f>
+        <v/>
       </c>
       <c r="K34" s="37">
         <f>SUM(G34:J34)</f>
         <v/>
       </c>
-      <c r="L34" s="18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>204.2</v>
-      </c>
-      <c r="N34" s="18" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="O34" s="18" t="n">
-        <v>911.2</v>
+      <c r="L34" s="18">
+        <f>IFERROR(L33,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="18">
+        <f>IFERROR(M33,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="18">
+        <f>IFERROR(N33,"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="18">
+        <f>IFERROR(O33,"")</f>
+        <v/>
       </c>
       <c r="P34" s="37">
         <f>SUM(L34:O34)</f>
         <v/>
       </c>
-      <c r="Q34" s="18" t="n">
-        <v>234.8</v>
-      </c>
-      <c r="R34" s="18" t="n">
-        <v>328.6</v>
-      </c>
-      <c r="S34" s="18" t="n">
-        <v>280.4</v>
-      </c>
-      <c r="T34" s="18" t="n">
-        <v>1479.1</v>
+      <c r="Q34" s="18">
+        <f>IFERROR(Q33,"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="18">
+        <f>IFERROR(R33,"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="18">
+        <f>IFERROR(S33,"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="18">
+        <f>IFERROR(T33,"")</f>
+        <v/>
       </c>
       <c r="U34" s="37">
         <f>SUM(Q34:T34)</f>
         <v/>
       </c>
-      <c r="V34" s="18" t="n">
-        <v>408.7</v>
-      </c>
-      <c r="W34" s="18" t="n">
-        <v>488.2</v>
-      </c>
-      <c r="X34" s="18" t="n">
-        <v>665.9</v>
-      </c>
-      <c r="Y34" s="20" t="n">
-        <v>1314.7</v>
+      <c r="V34" s="18">
+        <f>IFERROR(V33,"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="18">
+        <f>IFERROR(W33,"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="18">
+        <f>IFERROR(X33,"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="20">
+        <f>IFERROR((Y20-(674.95)*(1.0))*100/Y32,"")</f>
+        <v/>
       </c>
       <c r="Z34" s="37">
         <f>SUM(V34:Y34)</f>
         <v/>
       </c>
-      <c r="AA34" s="18" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="AB34" s="19" t="n">
-        <v>939.6</v>
+      <c r="AA34" s="18">
+        <f>IFERROR(AA33,"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="19">
+        <f>IFERROR(AB33,"")</f>
+        <v/>
       </c>
       <c r="AC34" s="20">
-        <f>IFERROR(X34*(1+변수!AC41),"")</f>
+        <f>IFERROR(AC33,"")</f>
         <v/>
       </c>
       <c r="AD34" s="20">
-        <f>IFERROR(Y34*(1+변수!AD41),"")</f>
+        <f>IFERROR(AD33,"")</f>
         <v/>
       </c>
       <c r="AE34" s="38">
@@ -32095,19 +31852,19 @@
         <v/>
       </c>
       <c r="AF34" s="20">
-        <f>IFERROR(AA34*(1+변수!AF41),"")</f>
+        <f>IFERROR(AF33,"")</f>
         <v/>
       </c>
       <c r="AG34" s="20">
-        <f>IFERROR(AB34*(1+변수!AG41),"")</f>
+        <f>IFERROR(AG33,"")</f>
         <v/>
       </c>
       <c r="AH34" s="20">
-        <f>IFERROR(AC34*(1+변수!AH41),"")</f>
+        <f>IFERROR(AH33,"")</f>
         <v/>
       </c>
       <c r="AI34" s="20">
-        <f>IFERROR(AD34*(1+변수!AI41),"")</f>
+        <f>IFERROR(AI33,"")</f>
         <v/>
       </c>
       <c r="AJ34" s="38">
@@ -32115,19 +31872,19 @@
         <v/>
       </c>
       <c r="AK34" s="20">
-        <f>IFERROR(AF34*(1+변수!AK41),"")</f>
+        <f>IFERROR(AK33,"")</f>
         <v/>
       </c>
       <c r="AL34" s="20">
-        <f>IFERROR(AG34*(1+변수!AL41),"")</f>
+        <f>IFERROR(AL33,"")</f>
         <v/>
       </c>
       <c r="AM34" s="20">
-        <f>IFERROR(AH34*(1+변수!AM41),"")</f>
+        <f>IFERROR(AM33,"")</f>
         <v/>
       </c>
       <c r="AN34" s="20">
-        <f>IFERROR(AI34*(1+변수!AN41),"")</f>
+        <f>IFERROR(AN33,"")</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -32376,7 +32133,7 @@
       <c r="AB36" s="19" t="n"/>
       <c r="AC36" s="20" t="n"/>
       <c r="AD36" s="20">
-        <f>변수!AD42</f>
+        <f>변수!AD41</f>
         <v/>
       </c>
       <c r="AE36" s="38">
@@ -32387,7 +32144,7 @@
       <c r="AG36" s="20" t="n"/>
       <c r="AH36" s="20" t="n"/>
       <c r="AI36" s="20">
-        <f>변수!AI42</f>
+        <f>변수!AI41</f>
         <v/>
       </c>
       <c r="AJ36" s="38">
@@ -32398,7 +32155,7 @@
       <c r="AL36" s="20" t="n"/>
       <c r="AM36" s="20" t="n"/>
       <c r="AN36" s="20">
-        <f>변수!AN42</f>
+        <f>변수!AN41</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -32515,11 +32272,11 @@
         <v/>
       </c>
       <c r="AC37" s="39">
-        <f>IFERROR(변수!$D$45/(Y33+AA33+AB33+AC33),"")</f>
+        <f>IFERROR(변수!$D$44/(Y33+AA33+AB33+AC33),"")</f>
         <v/>
       </c>
       <c r="AD37" s="39">
-        <f>IFERROR(변수!$D$45/(AA33+AB33+AC33+AD33),"")</f>
+        <f>IFERROR(변수!$D$44/(AA33+AB33+AC33+AD33),"")</f>
         <v/>
       </c>
       <c r="AE37" s="40">
@@ -32527,19 +32284,19 @@
         <v/>
       </c>
       <c r="AF37" s="39">
-        <f>IFERROR(변수!$D$45/(AB33+AC33+AD33+AF33),"")</f>
+        <f>IFERROR(변수!$D$44/(AB33+AC33+AD33+AF33),"")</f>
         <v/>
       </c>
       <c r="AG37" s="39">
-        <f>IFERROR(변수!$D$45/(AC33+AD33+AF33+AG33),"")</f>
+        <f>IFERROR(변수!$D$44/(AC33+AD33+AF33+AG33),"")</f>
         <v/>
       </c>
       <c r="AH37" s="39">
-        <f>IFERROR(변수!$D$45/(AD33+AF33+AG33+AH33),"")</f>
+        <f>IFERROR(변수!$D$44/(AD33+AF33+AG33+AH33),"")</f>
         <v/>
       </c>
       <c r="AI37" s="39">
-        <f>IFERROR(변수!$D$45/(AF33+AG33+AH33+AI33),"")</f>
+        <f>IFERROR(변수!$D$44/(AF33+AG33+AH33+AI33),"")</f>
         <v/>
       </c>
       <c r="AJ37" s="40">
@@ -32547,19 +32304,19 @@
         <v/>
       </c>
       <c r="AK37" s="39">
-        <f>IFERROR(변수!$D$45/(AG33+AH33+AI33+AK33),"")</f>
+        <f>IFERROR(변수!$D$44/(AG33+AH33+AI33+AK33),"")</f>
         <v/>
       </c>
       <c r="AL37" s="39">
-        <f>IFERROR(변수!$D$45/(AH33+AI33+AK33+AL33),"")</f>
+        <f>IFERROR(변수!$D$44/(AH33+AI33+AK33+AL33),"")</f>
         <v/>
       </c>
       <c r="AM37" s="39">
-        <f>IFERROR(변수!$D$45/(AI33+AK33+AL33+AM33),"")</f>
+        <f>IFERROR(변수!$D$44/(AI33+AK33+AL33+AM33),"")</f>
         <v/>
       </c>
       <c r="AN37" s="39">
-        <f>IFERROR(변수!$D$45/(AK33+AL33+AM33+AN33),"")</f>
+        <f>IFERROR(변수!$D$44/(AK33+AL33+AM33+AN33),"")</f>
         <v/>
       </c>
       <c r="AO37" s="40">
@@ -32685,11 +32442,11 @@
         <v/>
       </c>
       <c r="AC38" s="39">
-        <f>IFERROR(변수!$D$45/AC35,"")</f>
+        <f>IFERROR(변수!$D$44/AC35,"")</f>
         <v/>
       </c>
       <c r="AD38" s="39">
-        <f>IFERROR(변수!$D$45/AD35,"")</f>
+        <f>IFERROR(변수!$D$44/AD35,"")</f>
         <v/>
       </c>
       <c r="AE38" s="40">
@@ -32697,19 +32454,19 @@
         <v/>
       </c>
       <c r="AF38" s="39">
-        <f>IFERROR(변수!$D$45/AF35,"")</f>
+        <f>IFERROR(변수!$D$44/AF35,"")</f>
         <v/>
       </c>
       <c r="AG38" s="39">
-        <f>IFERROR(변수!$D$45/AG35,"")</f>
+        <f>IFERROR(변수!$D$44/AG35,"")</f>
         <v/>
       </c>
       <c r="AH38" s="39">
-        <f>IFERROR(변수!$D$45/AH35,"")</f>
+        <f>IFERROR(변수!$D$44/AH35,"")</f>
         <v/>
       </c>
       <c r="AI38" s="39">
-        <f>IFERROR(변수!$D$45/AI35,"")</f>
+        <f>IFERROR(변수!$D$44/AI35,"")</f>
         <v/>
       </c>
       <c r="AJ38" s="40">
@@ -32717,19 +32474,19 @@
         <v/>
       </c>
       <c r="AK38" s="39">
-        <f>IFERROR(변수!$D$45/AK35,"")</f>
+        <f>IFERROR(변수!$D$44/AK35,"")</f>
         <v/>
       </c>
       <c r="AL38" s="39">
-        <f>IFERROR(변수!$D$45/AL35,"")</f>
+        <f>IFERROR(변수!$D$44/AL35,"")</f>
         <v/>
       </c>
       <c r="AM38" s="39">
-        <f>IFERROR(변수!$D$45/AM35,"")</f>
+        <f>IFERROR(변수!$D$44/AM35,"")</f>
         <v/>
       </c>
       <c r="AN38" s="39">
-        <f>IFERROR(변수!$D$45/AN35,"")</f>
+        <f>IFERROR(변수!$D$44/AN35,"")</f>
         <v/>
       </c>
       <c r="AO38" s="40">
@@ -33763,7 +33520,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
       <c r="W2" s="42" t="n"/>
@@ -39152,7 +38909,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
       <c r="I2" s="42" t="n"/>
@@ -41007,7 +40764,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
     </row>
@@ -41018,7 +40775,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -41195,7 +40952,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D51+F7*(1-변수!D51),"")</f>
+        <f>IFERROR(E7*변수!D50+F7*(1-변수!D50),"")</f>
         <v/>
       </c>
     </row>
@@ -41206,7 +40963,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -41230,7 +40987,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -41254,7 +41011,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D50</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -41318,7 +41075,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -43126,7 +42883,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D58</f>
+        <f>변수!D57</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42850</v>
+        <v>42800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>46560</v>
+        <v>46550</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,11 +9455,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>42850</v>
+        <v>42800</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,000원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9769,7 +9769,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05928745488891241</v>
+        <v>0.05928745488891243</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.05214443690966399</v>
+        <v>0.05214443690966394</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01681726185905052</v>
+        <v>0.01681726185905281</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42800</v>
+        <v>40550</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6347,7 +6347,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>42550</v>
+        <v>40250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>46550</v>
+        <v>45550</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>42800</v>
+        <v>40550</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.34</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="32">
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>40550</v>
+        <v>40200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6347,7 +6347,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>40250</v>
+        <v>37400</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>45550</v>
+        <v>44764.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,11 +9455,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>40550</v>
+        <v>40200</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,800원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.74</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="32">
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>40200</v>
+        <v>42900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>44764.3</v>
+        <v>44525</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,11 +9455,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>40200</v>
+        <v>42900</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 42,800원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 40,550원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.65</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="32">
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>42900</v>
+        <v>41950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>44525</v>
+        <v>43568.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,11 +9455,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>42900</v>
+        <v>41950</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 40,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 40,250원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.36</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32">
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/071970_model.xlsx
+++ b/argus/kship/models/071970_model.xlsx
@@ -4319,7 +4319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5197,35 +5197,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5316,35 +5316,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5435,35 +5435,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5554,35 +5554,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5673,35 +5673,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5792,35 +5792,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5911,35 +5911,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6030,35 +6030,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6165,7 +6165,7 @@
         <v>48700</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>41950</v>
+        <v>34650</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6347,7 +6347,7 @@
         <v>46500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6438,7 +6438,7 @@
         <v>54832.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>43568.2</v>
+        <v>41559.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9455,11 +9455,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>41950</v>
+        <v>34650</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 40,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 37,450원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.11</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="32">
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="33">
